--- a/Document/操作方法/拡張機能など.xlsx
+++ b/Document/操作方法/拡張機能など.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\StudyLogs\Document\操作方法\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02843823-8D21-4C9B-8030-A614E4238296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CCE0C76-A672-42D6-B020-323D1C33395E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="3900" windowWidth="28170" windowHeight="14655" xr2:uid="{A16775A2-4027-400C-B82D-18BC41AEE9E7}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{A16775A2-4027-400C-B82D-18BC41AEE9E7}"/>
   </bookViews>
   <sheets>
     <sheet name="変更履歴" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>ClosedXML</t>
   </si>
@@ -95,6 +95,19 @@
     <t>作成</t>
     <rPh sb="0" eb="2">
       <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バージョンを変えたらversionの番号を変えること</t>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>バンゴウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -384,6 +397,50 @@
         <a:xfrm>
           <a:off x="666750" y="23088600"/>
           <a:ext cx="4086795" cy="5639587"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>248546</xdr:colOff>
+      <xdr:row>153</xdr:row>
+      <xdr:rowOff>191258</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD69E754-FCF1-3CE2-8E21-FF0AE8F27CBD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="31194375"/>
+          <a:ext cx="6420746" cy="5430008"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -787,7 +844,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85A19109-3167-4AEA-A630-E2C06EAD7D88}">
-  <dimension ref="B2:B3"/>
+  <dimension ref="B2:B131"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.4">
@@ -798,6 +855,11 @@
     <row r="3" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B131" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
